--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651329</v>
+        <v>124652178</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596804</v>
+        <v>596843</v>
       </c>
       <c r="R3" t="n">
-        <v>6924072</v>
+        <v>6923997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651598</v>
+        <v>124651851</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596820</v>
+        <v>596826</v>
       </c>
       <c r="R4" t="n">
-        <v>6924013</v>
+        <v>6924026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652178</v>
+        <v>124651329</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596843</v>
+        <v>596804</v>
       </c>
       <c r="R5" t="n">
-        <v>6923997</v>
+        <v>6924072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651851</v>
+        <v>124651598</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596826</v>
+        <v>596820</v>
       </c>
       <c r="R6" t="n">
-        <v>6924026</v>
+        <v>6924013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R3" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R4" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651329</v>
+        <v>124651598</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596804</v>
+        <v>596820</v>
       </c>
       <c r="R5" t="n">
-        <v>6924072</v>
+        <v>6924013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651598</v>
+        <v>124651329</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596820</v>
+        <v>596804</v>
       </c>
       <c r="R6" t="n">
-        <v>6924013</v>
+        <v>6924072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651851</v>
+        <v>124651526</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596826</v>
+        <v>596820</v>
       </c>
       <c r="R3" t="n">
-        <v>6924026</v>
+        <v>6924013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R4" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651598</v>
+        <v>124652178</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596820</v>
+        <v>596843</v>
       </c>
       <c r="R5" t="n">
-        <v>6924013</v>
+        <v>6923997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651526</v>
+        <v>124651598</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651851</v>
+        <v>124651329</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596826</v>
+        <v>596804</v>
       </c>
       <c r="R4" t="n">
-        <v>6924026</v>
+        <v>6924072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R5" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651329</v>
+        <v>124652178</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596804</v>
+        <v>596843</v>
       </c>
       <c r="R6" t="n">
-        <v>6924072</v>
+        <v>6923997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651598</v>
+        <v>124651526</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651329</v>
+        <v>124651851</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596804</v>
+        <v>596826</v>
       </c>
       <c r="R4" t="n">
-        <v>6924072</v>
+        <v>6924026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651851</v>
+        <v>124651329</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596826</v>
+        <v>596804</v>
       </c>
       <c r="R5" t="n">
-        <v>6924026</v>
+        <v>6924072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,474 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124939545</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596907</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6923936</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124939633</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596916</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6923900</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124939538</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596884</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6923933</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124939374</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596875</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6923944</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651526</v>
+        <v>124651598</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R4" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651329</v>
+        <v>124651851</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596804</v>
+        <v>596826</v>
       </c>
       <c r="R5" t="n">
-        <v>6924072</v>
+        <v>6924026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124652178</v>
+        <v>124651329</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596843</v>
+        <v>596804</v>
       </c>
       <c r="R6" t="n">
-        <v>6923997</v>
+        <v>6924072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939545</v>
+        <v>124939374</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,31 +1254,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1287,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596907</v>
+        <v>596875</v>
       </c>
       <c r="R7" t="n">
-        <v>6923936</v>
+        <v>6923944</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,34 +1380,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939538</v>
+        <v>124939545</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1497,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596884</v>
+        <v>596907</v>
       </c>
       <c r="R9" t="n">
-        <v>6923933</v>
+        <v>6923936</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,51 +1610,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R10" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651598</v>
+        <v>124652178</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596820</v>
+        <v>596843</v>
       </c>
       <c r="R3" t="n">
-        <v>6924013</v>
+        <v>6923997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652178</v>
+        <v>124651329</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596843</v>
+        <v>596804</v>
       </c>
       <c r="R4" t="n">
-        <v>6923997</v>
+        <v>6924072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651851</v>
+        <v>124651598</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596826</v>
+        <v>596820</v>
       </c>
       <c r="R5" t="n">
-        <v>6924026</v>
+        <v>6924013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651329</v>
+        <v>124651851</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596804</v>
+        <v>596826</v>
       </c>
       <c r="R6" t="n">
-        <v>6924072</v>
+        <v>6924026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,51 +1254,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939538</v>
+        <v>124939545</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,39 +1370,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596884</v>
+        <v>596907</v>
       </c>
       <c r="R8" t="n">
-        <v>6923933</v>
+        <v>6923936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939545</v>
+        <v>124939374</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,31 +1483,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,13 +1521,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596907</v>
+        <v>596875</v>
       </c>
       <c r="R9" t="n">
-        <v>6923936</v>
+        <v>6923944</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,34 +1609,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R10" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651329</v>
+        <v>124651598</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596804</v>
+        <v>596820</v>
       </c>
       <c r="R4" t="n">
-        <v>6924072</v>
+        <v>6924013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651598</v>
+        <v>124651851</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596820</v>
+        <v>596826</v>
       </c>
       <c r="R5" t="n">
-        <v>6924013</v>
+        <v>6924026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651851</v>
+        <v>124651329</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596826</v>
+        <v>596804</v>
       </c>
       <c r="R6" t="n">
-        <v>6924026</v>
+        <v>6924072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R7" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939545</v>
+        <v>124939633</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1375,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596907</v>
+        <v>596916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923936</v>
+        <v>6923900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939374</v>
+        <v>124939545</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,36 +1483,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1521,13 +1516,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596875</v>
+        <v>596907</v>
       </c>
       <c r="R9" t="n">
-        <v>6923944</v>
+        <v>6923936</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939538</v>
+        <v>124939374</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,46 +1600,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596884</v>
+        <v>596875</v>
       </c>
       <c r="R10" t="n">
-        <v>6923933</v>
+        <v>6923944</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R3" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651598</v>
+        <v>124651329</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596820</v>
+        <v>596804</v>
       </c>
       <c r="R4" t="n">
-        <v>6924013</v>
+        <v>6924072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R5" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651329</v>
+        <v>124651598</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596804</v>
+        <v>596820</v>
       </c>
       <c r="R6" t="n">
-        <v>6924072</v>
+        <v>6924013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939538</v>
+        <v>124939633</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,39 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596884</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923933</v>
+        <v>6923900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,34 +1370,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939545</v>
+        <v>124939538</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1487,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596907</v>
+        <v>596884</v>
       </c>
       <c r="R9" t="n">
-        <v>6923936</v>
+        <v>6923933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,12 +1576,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651851</v>
+        <v>124651598</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596826</v>
+        <v>596820</v>
       </c>
       <c r="R3" t="n">
-        <v>6924026</v>
+        <v>6924013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651329</v>
+        <v>124652178</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596804</v>
+        <v>596843</v>
       </c>
       <c r="R4" t="n">
-        <v>6924072</v>
+        <v>6923997</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652178</v>
+        <v>124651329</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596843</v>
+        <v>596804</v>
       </c>
       <c r="R5" t="n">
-        <v>6923997</v>
+        <v>6924072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651598</v>
+        <v>124651851</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596820</v>
+        <v>596826</v>
       </c>
       <c r="R6" t="n">
-        <v>6924013</v>
+        <v>6924026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939633</v>
+        <v>124939374</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,41 +1254,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>596875</v>
       </c>
       <c r="R7" t="n">
-        <v>6923900</v>
+        <v>6923944</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939545</v>
+        <v>124939633</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1380,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596907</v>
+        <v>596916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923936</v>
+        <v>6923900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1464,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939538</v>
+        <v>124939545</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1492,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596884</v>
+        <v>596907</v>
       </c>
       <c r="R9" t="n">
-        <v>6923933</v>
+        <v>6923936</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939374</v>
+        <v>124939538</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,51 +1605,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596875</v>
+        <v>596884</v>
       </c>
       <c r="R10" t="n">
-        <v>6923944</v>
+        <v>6923933</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651598</v>
+        <v>124651526</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R4" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R6" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,51 +1254,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939374</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,41 +1366,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596875</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923944</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651526</v>
+        <v>124652178</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596820</v>
+        <v>596843</v>
       </c>
       <c r="R3" t="n">
-        <v>6924013</v>
+        <v>6923997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124652178</v>
+        <v>124651598</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596843</v>
+        <v>596820</v>
       </c>
       <c r="R6" t="n">
-        <v>6923997</v>
+        <v>6924013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R7" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,51 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939545</v>
+        <v>124939538</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,39 +1487,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596907</v>
+        <v>596884</v>
       </c>
       <c r="R9" t="n">
-        <v>6923936</v>
+        <v>6923933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939538</v>
+        <v>124939374</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,46 +1600,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596884</v>
+        <v>596875</v>
       </c>
       <c r="R10" t="n">
-        <v>6923933</v>
+        <v>6923944</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652178</v>
+        <v>124651526</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596843</v>
+        <v>596820</v>
       </c>
       <c r="R3" t="n">
-        <v>6923997</v>
+        <v>6924013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651851</v>
+        <v>124651329</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596826</v>
+        <v>596804</v>
       </c>
       <c r="R4" t="n">
-        <v>6924026</v>
+        <v>6924072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651329</v>
+        <v>124652178</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596804</v>
+        <v>596843</v>
       </c>
       <c r="R5" t="n">
-        <v>6924072</v>
+        <v>6923997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651598</v>
+        <v>124651851</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596820</v>
+        <v>596826</v>
       </c>
       <c r="R6" t="n">
-        <v>6924013</v>
+        <v>6924026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,34 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1464,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939538</v>
+        <v>124939633</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1492,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596884</v>
+        <v>596916</v>
       </c>
       <c r="R9" t="n">
-        <v>6923933</v>
+        <v>6923900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,12 +1576,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651329</v>
+        <v>124651851</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596804</v>
+        <v>596826</v>
       </c>
       <c r="R4" t="n">
-        <v>6924072</v>
+        <v>6924026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651851</v>
+        <v>124651329</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596826</v>
+        <v>596804</v>
       </c>
       <c r="R6" t="n">
-        <v>6924026</v>
+        <v>6924072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939538</v>
+        <v>124939633</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,39 +1375,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596884</v>
+        <v>596916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923933</v>
+        <v>6923900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,34 +1487,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R9" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,12 +1576,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651526</v>
+        <v>124651329</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596820</v>
+        <v>596804</v>
       </c>
       <c r="R3" t="n">
-        <v>6924013</v>
+        <v>6924072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651851</v>
+        <v>124651526</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596826</v>
+        <v>596820</v>
       </c>
       <c r="R4" t="n">
-        <v>6924026</v>
+        <v>6924013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R5" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651329</v>
+        <v>124652178</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596804</v>
+        <v>596843</v>
       </c>
       <c r="R6" t="n">
-        <v>6924072</v>
+        <v>6923997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939545</v>
+        <v>124939633</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,39 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596907</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923936</v>
+        <v>6923900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,34 +1370,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,12 +1459,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651526</v>
+        <v>124651598</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning.</t>
+          <t>Ser ut som spelspillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1056,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R5" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124652178</v>
+        <v>124651851</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596843</v>
+        <v>596826</v>
       </c>
       <c r="R6" t="n">
-        <v>6923997</v>
+        <v>6924026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R7" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939545</v>
+        <v>124939538</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596907</v>
+        <v>596884</v>
       </c>
       <c r="R8" t="n">
-        <v>6923936</v>
+        <v>6923933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1464,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939538</v>
+        <v>124939633</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1492,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596884</v>
+        <v>596916</v>
       </c>
       <c r="R9" t="n">
-        <v>6923933</v>
+        <v>6923900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,12 +1576,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651329</v>
+        <v>124651851</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596804</v>
+        <v>596826</v>
       </c>
       <c r="R3" t="n">
-        <v>6924072</v>
+        <v>6924026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>124651598</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652178</v>
+        <v>124651329</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596843</v>
+        <v>596804</v>
       </c>
       <c r="R5" t="n">
-        <v>6923997</v>
+        <v>6924072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124651851</v>
+        <v>124652178</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596826</v>
+        <v>596843</v>
       </c>
       <c r="R6" t="n">
-        <v>6924026</v>
+        <v>6923997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939545</v>
+        <v>124939374</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,31 +1254,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1287,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596907</v>
+        <v>596875</v>
       </c>
       <c r="R7" t="n">
-        <v>6923936</v>
+        <v>6923944</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939538</v>
+        <v>124939633</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,39 +1380,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596884</v>
+        <v>596916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923933</v>
+        <v>6923900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,22 +1464,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939633</v>
+        <v>124939538</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,34 +1492,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596916</v>
+        <v>596884</v>
       </c>
       <c r="R9" t="n">
-        <v>6923900</v>
+        <v>6923933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939374</v>
+        <v>124939545</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,36 +1605,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596875</v>
+        <v>596907</v>
       </c>
       <c r="R10" t="n">
-        <v>6923944</v>
+        <v>6923936</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,51 +1254,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,34 +1370,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R8" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,12 +1459,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939545</v>
+        <v>124939374</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,31 +1600,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596907</v>
+        <v>596875</v>
       </c>
       <c r="R10" t="n">
-        <v>6923936</v>
+        <v>6923944</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1242,15 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939633</v>
+        <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,34 +1253,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596916</v>
+        <v>596907</v>
       </c>
       <c r="R7" t="n">
-        <v>6923900</v>
+        <v>6923936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,27 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939545</v>
+        <v>124939538</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,39 +1365,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596907</v>
+        <v>596884</v>
       </c>
       <c r="R8" t="n">
-        <v>6923936</v>
+        <v>6923933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,70 +1454,70 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939538</v>
+        <v>124939374</v>
       </c>
       <c r="B9" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596884</v>
+        <v>596875</v>
       </c>
       <c r="R9" t="n">
-        <v>6923933</v>
+        <v>6923944</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,75 +1571,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939374</v>
+        <v>124939633</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596875</v>
+        <v>596916</v>
       </c>
       <c r="R10" t="n">
-        <v>6923944</v>
+        <v>6923900</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
         <v>124939545</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124425674</v>
+        <v>124939633</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596864</v>
+        <v>596916</v>
       </c>
       <c r="R2" t="n">
-        <v>6923952</v>
+        <v>6923900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124651851</v>
+        <v>124939545</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596826</v>
+        <v>596907</v>
       </c>
       <c r="R3" t="n">
-        <v>6924026</v>
+        <v>6923936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,70 +882,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124651598</v>
+        <v>124938929</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596820</v>
+        <v>596800</v>
       </c>
       <c r="R4" t="n">
-        <v>6924013</v>
+        <v>6923924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,17 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ser ut som spelspillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,70 +999,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124651329</v>
+        <v>124940144</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596804</v>
+        <v>596974</v>
       </c>
       <c r="R5" t="n">
-        <v>6924072</v>
+        <v>6923946</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,17 +1081,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124652178</v>
+        <v>124425674</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,24 +1157,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596843</v>
+        <v>596864</v>
       </c>
       <c r="R6" t="n">
-        <v>6923997</v>
+        <v>6923952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,17 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,50 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939545</v>
+        <v>124651329</v>
       </c>
       <c r="B7" t="n">
-        <v>57681</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596907</v>
+        <v>596804</v>
       </c>
       <c r="R7" t="n">
-        <v>6923936</v>
+        <v>6924072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,22 +1303,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färskspillning. Ser ut som spelspillning. Kort och vit i ena änden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,62 +1328,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939538</v>
+        <v>124651526</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596884</v>
+        <v>596820</v>
       </c>
       <c r="R8" t="n">
-        <v>6923933</v>
+        <v>6924013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,22 +1413,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ser ut som spelspillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939374</v>
+        <v>124651851</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,29 +1479,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596875</v>
+        <v>596826</v>
       </c>
       <c r="R9" t="n">
-        <v>6923944</v>
+        <v>6924026</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,22 +1523,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ser ut som spelspillning. Flera högar. Färskt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,57 +1548,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124939633</v>
+        <v>124652178</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596916</v>
+        <v>596843</v>
       </c>
       <c r="R10" t="n">
-        <v>6923900</v>
+        <v>6923997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,22 +1633,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:27</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ser ut som spelspillnig. Färsk. Flera högar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,15 +1658,244 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124939374</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6923944</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124939538</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596884</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6923933</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16319-2025 artfynd.xlsx
+++ b/artfynd/A 16319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124939633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124939545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124938929</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124940144</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124425674</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124651329</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124651526</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124651851</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124652178</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124939374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,8 +1951,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124939538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>